--- a/reports/qa_evaluation/report.xlsx
+++ b/reports/qa_evaluation/report.xlsx
@@ -1022,7 +1022,7 @@
         <v>6</v>
       </c>
       <c r="B3" s="3">
-        <v>71.90000000000001</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>7</v>
